--- a/KeePassKeyFileGenerator(Excel).xlsx
+++ b/KeePassKeyFileGenerator(Excel).xlsx
@@ -2,23 +2,23 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gabeweb\Documentos\Personal\Security\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8110963C-0D82-48D4-B970-772412970D1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD3CF9AE-7C76-4EB9-81BB-D590928547A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{6877E4AE-4832-4833-9901-BCE28557DB92}"/>
   </bookViews>
   <sheets>
     <sheet name="KeePass_KeyFile" sheetId="2" r:id="rId1"/>
-    <sheet name="Creditos" sheetId="4" r:id="rId2"/>
+    <sheet name="About" sheetId="4" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="LETRAS_HEX">KeePass_KeyFile!$Q$6:$Q$11</definedName>
-    <definedName name="NUMEROS_HEX">KeePass_KeyFile!$O$6:$O$15</definedName>
+    <definedName name="LETRAS_HEX">KeePass_KeyFile!$T$6:$T$11</definedName>
+    <definedName name="NUMEROS_HEX">KeePass_KeyFile!$R$6:$R$15</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -63,10 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="33">
-  <si>
-    <t>https://keepass.info/help/base/keys.html#keyfiles:~:text=XML%20%28recommended%2C%20default%29%2E</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="41">
   <si>
     <t>This XML structure is generated according to the official specifications to create key files for KeePass:</t>
   </si>
@@ -175,20 +172,183 @@
     <t>As a registered user, you have the right to copy and modify or adapt this book only for personal use, while for other purposes you must first express it to its author.</t>
   </si>
   <si>
-    <t>This workbook (KeePass KeyFile Generator) is for personal use only and its copying, either in whole or in part, for resale without prior notification to its author is totally prohibited.</t>
-  </si>
-  <si>
     <t>You can also request a "pre-personalized" copy of crypFarm with predefined patterns and formulas according to your needs.</t>
   </si>
   <si>
     <t>Thank you for give a try to KeePass KeyFile Generator</t>
+  </si>
+  <si>
+    <t>2) Copy XML</t>
+  </si>
+  <si>
+    <t>3) Save File</t>
+  </si>
+  <si>
+    <t>4) Use in KeePass</t>
+  </si>
+  <si>
+    <t>1) Press F9 Key</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Just press the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFF8F8F8"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>F9</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFF8F8F8"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> key to generate a new Data Key and its respective Hash.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Select and copy the generated XML text in </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFF8F8F8"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Column D</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFF8F8F8"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Paste into your favorite text editor and save as </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFF8F8F8"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>MyKey.keyx</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFF8F8F8"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (UTF-8 encoding).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Load your </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFF8F8F8"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.keyx file</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFF8F8F8"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> when creating or unlocking your database.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFF453A"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>📌</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFF8F8F8"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> How to Generate a KeePass KeyFile (.keyx)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>This workbook (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFF8F8F8"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>KeePass KeyFile Generator</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFF8F8F8"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>) is for personal use only and its copying, either in whole or in part, for resale without prior notification to its author is totally prohibited.</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -213,14 +373,6 @@
       <u/>
       <sz val="11"/>
       <color theme="10"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF708FEA"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -317,19 +469,29 @@
       <family val="2"/>
       <scheme val="major"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FFFF453A"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FFF8F8F8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="13">
+  <fills count="15">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF121212"/>
-        <bgColor rgb="FF121212"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -387,8 +549,26 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF141414"/>
+        <fgColor rgb="FF404040"/>
         <bgColor rgb="FF121212"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1"/>
+        <bgColor rgb="FF121212"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1"/>
+        <bgColor rgb="FF708FEA"/>
       </patternFill>
     </fill>
   </fills>
@@ -613,121 +793,132 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="3"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="4"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="11" fillId="5" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="11" fillId="5" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="centerContinuous" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="3"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="centerContinuous" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="centerContinuous" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="centerContinuous" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="4"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="centerContinuous" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="12" fillId="6" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" xfId="3" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="16" fillId="12" borderId="0" xfId="3" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" xfId="3" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="12" fillId="6" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="centerContinuous"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="0" xfId="3" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" xfId="3" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="12" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="12" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -741,8 +932,10 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFF8F8F8"/>
+      <color rgb="FFFF453A"/>
+      <color rgb="FF404040"/>
       <color rgb="FF141414"/>
-      <color rgb="FFF8F8F8"/>
     </mruColors>
   </colors>
   <extLst>
@@ -1126,60 +1319,94 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF734481-A090-402C-8041-CCAF92315AA3}">
-  <dimension ref="A1:Z19"/>
+  <sheetPr codeName="Hoja1"/>
+  <dimension ref="A1:AC19"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="30" customHeight="1" outlineLevelCol="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="66.125" style="34" customWidth="1"/>
-    <col min="2" max="2" width="6.25" style="34" customWidth="1"/>
-    <col min="3" max="12" width="13.25" style="34" customWidth="1" outlineLevel="1"/>
-    <col min="13" max="13" width="6.25" style="34" customWidth="1"/>
-    <col min="14" max="14" width="5.25" style="34" customWidth="1" outlineLevel="1"/>
-    <col min="15" max="15" width="13.25" style="34" customWidth="1" outlineLevel="1"/>
-    <col min="16" max="16" width="5.25" style="34" customWidth="1" outlineLevel="1"/>
-    <col min="17" max="17" width="13.25" style="34" customWidth="1" outlineLevel="1"/>
-    <col min="18" max="26" width="10.625" style="34" customWidth="1"/>
-    <col min="27" max="16384" width="11" style="35"/>
+    <col min="1" max="1" width="18.75" style="33" customWidth="1"/>
+    <col min="2" max="2" width="31.25" style="33" customWidth="1"/>
+    <col min="3" max="3" width="3.125" style="33" customWidth="1"/>
+    <col min="4" max="4" width="66.125" style="33" customWidth="1"/>
+    <col min="5" max="5" width="3.125" style="33" customWidth="1"/>
+    <col min="6" max="15" width="13.25" style="33" customWidth="1" outlineLevel="1"/>
+    <col min="16" max="16" width="6.25" style="33" customWidth="1"/>
+    <col min="17" max="17" width="5.25" style="33" customWidth="1" outlineLevel="1"/>
+    <col min="18" max="18" width="13.25" style="33" customWidth="1" outlineLevel="1"/>
+    <col min="19" max="19" width="5.25" style="33" customWidth="1" outlineLevel="1"/>
+    <col min="20" max="20" width="13.25" style="33" customWidth="1" outlineLevel="1"/>
+    <col min="21" max="29" width="10.625" style="33" customWidth="1"/>
+    <col min="30" max="16384" width="11" style="35"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" s="25" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="28" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="2" spans="1:17" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="39" t="s">
+    <row r="1" spans="1:21" s="39" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="26" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="4" spans="1:17" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="24" t="s">
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23"/>
+      <c r="H1" s="23"/>
+      <c r="I1" s="23"/>
+      <c r="J1" s="23"/>
+      <c r="K1" s="23"/>
+      <c r="L1" s="23"/>
+      <c r="M1" s="23"/>
+      <c r="N1" s="23"/>
+      <c r="O1" s="23"/>
+      <c r="P1" s="23"/>
+      <c r="Q1" s="23"/>
+      <c r="R1" s="23"/>
+      <c r="S1" s="23"/>
+      <c r="T1" s="23"/>
+      <c r="U1" s="23"/>
+    </row>
+    <row r="2" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="38" t="s">
         <v>21</v>
       </c>
-      <c r="C4" s="40" t="s">
+    </row>
+    <row r="4" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="45" t="s">
+        <v>39</v>
+      </c>
+      <c r="B4" s="45"/>
+      <c r="D4" s="22" t="s">
         <v>20</v>
       </c>
-      <c r="D4" s="40"/>
-      <c r="E4" s="40"/>
-      <c r="F4" s="40"/>
-      <c r="G4" s="40"/>
-      <c r="H4" s="40"/>
-      <c r="I4" s="40"/>
-      <c r="J4" s="40"/>
-      <c r="K4" s="40"/>
-      <c r="L4" s="40"/>
-      <c r="N4" s="41" t="s">
+      <c r="F4" s="43" t="s">
         <v>19</v>
       </c>
-      <c r="O4" s="41"/>
-      <c r="P4" s="41"/>
-      <c r="Q4" s="41"/>
-    </row>
-    <row r="5" spans="1:17" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="23" t="str" cm="1">
-        <f t="array" aca="1" ref="A5:A16" ca="1">_xlfn.LET(
+      <c r="G4" s="43"/>
+      <c r="H4" s="43"/>
+      <c r="I4" s="43"/>
+      <c r="J4" s="43"/>
+      <c r="K4" s="43"/>
+      <c r="L4" s="43"/>
+      <c r="M4" s="43"/>
+      <c r="N4" s="43"/>
+      <c r="O4" s="43"/>
+      <c r="Q4" s="44" t="s">
+        <v>18</v>
+      </c>
+      <c r="R4" s="44"/>
+      <c r="S4" s="44"/>
+      <c r="T4" s="44"/>
+    </row>
+    <row r="5" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="36" t="s">
+        <v>34</v>
+      </c>
+      <c r="B5" s="37" t="s">
+        <v>35</v>
+      </c>
+      <c r="D5" s="21" t="str" cm="1">
+        <f t="array" aca="1" ref="D5:D16" ca="1">_xlfn.LET(
    _xlpm.q, """",
-   _xlpm.Hash, D6,
-   _xlpm.rango,_xlfn.ANCHORARRAY( E6),
+   _xlpm.Hash, G6,
+   _xlpm.rango,_xlfn.ANCHORARRAY( H6),
    _xlpm.MyRow1, "        " &amp; _xlfn.TEXTJOIN(" ", 1, INDEX(_xlpm.rango, _xlfn.SEQUENCE(4,, 1))),
    _xlpm.MyRow2, "        " &amp; _xlfn.TEXTJOIN(" ", 1, INDEX(_xlpm.rango, _xlfn.SEQUENCE(4,, 5))),
    _xlfn.VSTACK(
@@ -1199,50 +1426,56 @@
 )</f>
         <v>&lt;?xml version="1.0" encoding="utf-8"?&gt;</v>
       </c>
-      <c r="D5" s="21" t="s">
-        <v>18</v>
-      </c>
-      <c r="E5" s="22" t="s">
+      <c r="G5" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="F5" s="22" t="s">
+      <c r="H5" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="G5" s="22" t="s">
+      <c r="I5" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="H5" s="22" t="s">
+      <c r="J5" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="I5" s="22" t="s">
+      <c r="K5" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="J5" s="22" t="s">
+      <c r="L5" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="K5" s="22" t="s">
+      <c r="M5" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="L5" s="22" t="s">
+      <c r="N5" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="N5" s="27"/>
-      <c r="O5" s="21" t="s">
+      <c r="O5" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="P5" s="27"/>
-      <c r="Q5" s="21" t="s">
+      <c r="Q5" s="25"/>
+      <c r="R5" s="19" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="6" spans="1:17" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="20" t="str">
+      <c r="S5" s="25"/>
+      <c r="T5" s="19" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="36" t="s">
+        <v>31</v>
+      </c>
+      <c r="B6" s="37" t="s">
+        <v>36</v>
+      </c>
+      <c r="D6" s="18" t="str">
         <f ca="1"/>
         <v>&lt;KeyFile&gt;</v>
       </c>
-      <c r="D6" s="19" t="str" cm="1">
-        <f t="array" aca="1" ref="D6" ca="1">_xlfn.LET(
-   _xlpm.inputText, _xlfn.TEXTJOIN("", 1,_xlfn.ANCHORARRAY( E6)),
+      <c r="G6" s="17" t="str" cm="1">
+        <f t="array" aca="1" ref="G6" ca="1">_xlfn.LET(
+   _xlpm.inputText, _xlfn.TEXTJOIN("", 1,_xlfn.ANCHORARRAY( H6)),
    IF(ISBLANK(_xlpm.inputText), "#NoValue",
       _xlfn.LET(
          _xlpm.cleanTxt_, SUBSTITUTE(_xlpm.inputText, " ", ""),
@@ -1299,53 +1532,53 @@
       )
    )
 )</f>
-        <v>4963A7DE</v>
-      </c>
-      <c r="E6" s="18" t="str" cm="1">
-        <f t="array" aca="1" ref="E6:L6" ca="1">_xlfn.LET(
+        <v>71F539A3</v>
+      </c>
+      <c r="H6" s="16" t="str" cm="1">
+        <f t="array" aca="1" ref="H6:O6" ca="1">_xlfn.LET(
     _xlpm.Pool, _xlfn.CONCAT(NUMEROS_HEX, LETRAS_HEX),
     _xlpm.Length, LEN(_xlpm.Pool),
     _xlfn.MAP(_xlfn.SEQUENCE(1, 8), _xlfn.LAMBDA(_xlpm.col,
         _xlfn.CONCAT(_xlfn.MAP(_xlfn.SEQUENCE(8), _xlfn.LAMBDA(_xlpm.lin, MID(_xlpm.Pool, RANDBETWEEN(1, _xlpm.Length), 1))))
     ))
 )</f>
-        <v>3C8DB034</v>
-      </c>
-      <c r="F6" s="18" t="str">
-        <f ca="1"/>
-        <v>8DD2D442</v>
-      </c>
-      <c r="G6" s="18" t="str">
-        <f ca="1"/>
-        <v>27DF7413</v>
-      </c>
-      <c r="H6" s="18" t="str">
-        <f ca="1"/>
-        <v>F52EABB4</v>
-      </c>
-      <c r="I6" s="18" t="str">
-        <f ca="1"/>
-        <v>4E7C14CD</v>
-      </c>
-      <c r="J6" s="18" t="str">
-        <f ca="1"/>
-        <v>E65BB751</v>
-      </c>
-      <c r="K6" s="18" t="str">
-        <f ca="1"/>
-        <v>43BFAE5C</v>
-      </c>
-      <c r="L6" s="18" t="str">
-        <f ca="1"/>
-        <v>3C210173</v>
-      </c>
-      <c r="N6" s="36">
+        <v>7DAA2CA0</v>
+      </c>
+      <c r="I6" s="16" t="str">
+        <f ca="1"/>
+        <v>6E6846D8</v>
+      </c>
+      <c r="J6" s="16" t="str">
+        <f ca="1"/>
+        <v>D74ECABE</v>
+      </c>
+      <c r="K6" s="16" t="str">
+        <f ca="1"/>
+        <v>65B227FC</v>
+      </c>
+      <c r="L6" s="16" t="str">
+        <f ca="1"/>
+        <v>76401883</v>
+      </c>
+      <c r="M6" s="16" t="str">
+        <f ca="1"/>
+        <v>4B328BD2</v>
+      </c>
+      <c r="N6" s="16" t="str">
+        <f ca="1"/>
+        <v>C64DA80E</v>
+      </c>
+      <c r="O6" s="16" t="str">
+        <f ca="1"/>
+        <v>DCC12245</v>
+      </c>
+      <c r="Q6" s="40">
         <v>48</v>
       </c>
-      <c r="O6" s="37" t="str">
-        <f t="shared" ref="O6:O15" si="0">IFERROR(
+      <c r="R6" s="41" t="str">
+        <f t="shared" ref="R6:R15" si="0">IFERROR(
     SUBSTITUTE(
-        CHAR(N6),
+        CHAR(Q6),
         " ",
         ""
     ),
@@ -1353,390 +1586,404 @@
 )</f>
         <v>0</v>
       </c>
-      <c r="P6" s="36">
+      <c r="S6" s="40">
         <v>65</v>
       </c>
-      <c r="Q6" s="38" t="str">
-        <f t="shared" ref="Q6:Q11" si="1">CHAR(P6)</f>
+      <c r="T6" s="42" t="str">
+        <f t="shared" ref="T6:T11" si="1">CHAR(S6)</f>
         <v>A</v>
       </c>
     </row>
-    <row r="7" spans="1:17" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="5" t="str">
+    <row r="7" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="36" t="s">
+        <v>32</v>
+      </c>
+      <c r="B7" s="37" t="s">
+        <v>37</v>
+      </c>
+      <c r="D7" s="3" t="str">
         <f ca="1"/>
         <v xml:space="preserve">    &lt;Meta&gt;</v>
       </c>
-      <c r="C7" s="17" t="s">
-        <v>6</v>
-      </c>
-      <c r="D7" s="18" cm="1">
-        <f t="array" aca="1" ref="D7:L7" ca="1">LEN(D6:L6)</f>
+      <c r="F7" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="G7" s="16" cm="1">
+        <f t="array" aca="1" ref="G7:O7" ca="1">LEN(G6:O6)</f>
         <v>8</v>
       </c>
-      <c r="E7" s="18">
+      <c r="H7" s="16">
         <f ca="1"/>
         <v>8</v>
       </c>
-      <c r="F7" s="18">
+      <c r="I7" s="16">
         <f ca="1"/>
         <v>8</v>
       </c>
-      <c r="G7" s="18">
+      <c r="J7" s="16">
         <f ca="1"/>
         <v>8</v>
       </c>
-      <c r="H7" s="18">
+      <c r="K7" s="16">
         <f ca="1"/>
         <v>8</v>
       </c>
-      <c r="I7" s="18">
+      <c r="L7" s="16">
         <f ca="1"/>
         <v>8</v>
       </c>
-      <c r="J7" s="18">
+      <c r="M7" s="16">
         <f ca="1"/>
         <v>8</v>
       </c>
-      <c r="K7" s="18">
+      <c r="N7" s="16">
         <f ca="1"/>
         <v>8</v>
       </c>
-      <c r="L7" s="18">
+      <c r="O7" s="16">
         <f ca="1"/>
         <v>8</v>
       </c>
-      <c r="N7" s="36">
+      <c r="Q7" s="40">
         <v>49</v>
       </c>
-      <c r="O7" s="37" t="str">
+      <c r="R7" s="41" t="str">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="P7" s="36">
+      <c r="S7" s="40">
         <v>66</v>
       </c>
-      <c r="Q7" s="38" t="str">
+      <c r="T7" s="42" t="str">
         <f t="shared" si="1"/>
         <v>B</v>
       </c>
     </row>
-    <row r="8" spans="1:17" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="7" t="str">
+    <row r="8" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="36" t="s">
+        <v>33</v>
+      </c>
+      <c r="B8" s="37" t="s">
+        <v>38</v>
+      </c>
+      <c r="D8" s="5" t="str">
         <f ca="1"/>
         <v xml:space="preserve">        &lt;Version&gt;2.0&lt;/Version&gt;</v>
       </c>
-      <c r="C8" s="17" t="s">
-        <v>5</v>
-      </c>
-      <c r="D8" s="14" cm="1">
-        <f t="array" aca="1" ref="D8:L8" ca="1">IFERROR(ROUND((D7:L7*LOG(LEN(_xlfn.CONCAT(NUMEROS_HEX,LETRAS_HEX)))),2),"")</f>
+      <c r="F8" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="G8" s="12" cm="1">
+        <f t="array" aca="1" ref="G8:O8" ca="1">IFERROR(ROUND((G7:O7*LOG(LEN(_xlfn.CONCAT(NUMEROS_HEX,LETRAS_HEX)))),2),"")</f>
         <v>9.6300000000000008</v>
       </c>
-      <c r="E8" s="14">
+      <c r="H8" s="12">
         <f ca="1"/>
         <v>9.6300000000000008</v>
       </c>
-      <c r="F8" s="14">
+      <c r="I8" s="12">
         <f ca="1"/>
         <v>9.6300000000000008</v>
       </c>
-      <c r="G8" s="14">
+      <c r="J8" s="12">
         <f ca="1"/>
         <v>9.6300000000000008</v>
       </c>
-      <c r="H8" s="14">
+      <c r="K8" s="12">
         <f ca="1"/>
         <v>9.6300000000000008</v>
       </c>
-      <c r="I8" s="14">
+      <c r="L8" s="12">
         <f ca="1"/>
         <v>9.6300000000000008</v>
       </c>
-      <c r="J8" s="14">
+      <c r="M8" s="12">
         <f ca="1"/>
         <v>9.6300000000000008</v>
       </c>
-      <c r="K8" s="14">
+      <c r="N8" s="12">
         <f ca="1"/>
         <v>9.6300000000000008</v>
       </c>
-      <c r="L8" s="14">
+      <c r="O8" s="12">
         <f ca="1"/>
         <v>9.6300000000000008</v>
       </c>
-      <c r="N8" s="36">
+      <c r="Q8" s="40">
         <v>50</v>
       </c>
-      <c r="O8" s="37" t="str">
+      <c r="R8" s="41" t="str">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="P8" s="36">
+      <c r="S8" s="40">
         <v>67</v>
       </c>
-      <c r="Q8" s="38" t="str">
+      <c r="T8" s="42" t="str">
         <f t="shared" si="1"/>
         <v>C</v>
       </c>
     </row>
-    <row r="9" spans="1:17" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="5" t="str">
+    <row r="9" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D9" s="3" t="str">
         <f ca="1"/>
         <v xml:space="preserve">    &lt;/Meta&gt;</v>
       </c>
-      <c r="C9" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="D9" s="15" cm="1">
-        <f t="array" aca="1" ref="D9:L9" ca="1">D7:L7*4.9231</f>
+      <c r="F9" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="G9" s="13" cm="1">
+        <f t="array" aca="1" ref="G9:O9" ca="1">G7:O7*4.9231</f>
         <v>39.384799999999998</v>
       </c>
-      <c r="E9" s="14">
+      <c r="H9" s="12">
         <f ca="1"/>
         <v>39.384799999999998</v>
       </c>
-      <c r="F9" s="14">
+      <c r="I9" s="12">
         <f ca="1"/>
         <v>39.384799999999998</v>
       </c>
-      <c r="G9" s="14">
+      <c r="J9" s="12">
         <f ca="1"/>
         <v>39.384799999999998</v>
       </c>
-      <c r="H9" s="14">
+      <c r="K9" s="12">
         <f ca="1"/>
         <v>39.384799999999998</v>
       </c>
-      <c r="I9" s="14">
+      <c r="L9" s="12">
         <f ca="1"/>
         <v>39.384799999999998</v>
       </c>
-      <c r="J9" s="14">
+      <c r="M9" s="12">
         <f ca="1"/>
         <v>39.384799999999998</v>
       </c>
-      <c r="K9" s="14">
+      <c r="N9" s="12">
         <f ca="1"/>
         <v>39.384799999999998</v>
       </c>
-      <c r="L9" s="14">
+      <c r="O9" s="12">
         <f ca="1"/>
         <v>39.384799999999998</v>
       </c>
-      <c r="N9" s="36">
+      <c r="Q9" s="40">
         <v>51</v>
       </c>
-      <c r="O9" s="37" t="str">
+      <c r="R9" s="41" t="str">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="P9" s="36">
+      <c r="S9" s="40">
         <v>68</v>
       </c>
-      <c r="Q9" s="38" t="str">
+      <c r="T9" s="42" t="str">
         <f t="shared" si="1"/>
         <v>D</v>
       </c>
     </row>
-    <row r="10" spans="1:17" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="5" t="str">
+    <row r="10" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D10" s="3" t="str">
         <f ca="1"/>
         <v xml:space="preserve">    &lt;Key&gt;</v>
       </c>
-      <c r="D10" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="E10" s="13" t="str" cm="1">
-        <f t="array" aca="1" ref="E10" ca="1">_xlfn.LET(
-   _xlpm.rango,_xlfn.ANCHORARRAY( E6),
+      <c r="G10" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="H10" s="11" t="str" cm="1">
+        <f t="array" aca="1" ref="H10" ca="1">_xlfn.LET(
+   _xlpm.rango,_xlfn.ANCHORARRAY( H6),
    _xlpm.MyRow1, _xlfn.TEXTJOIN(" ", 1, INDEX(_xlpm.rango, _xlfn.SEQUENCE(4,, 1))),
    _xlpm.MyRow2, _xlfn.TEXTJOIN(" ", 1, INDEX(_xlpm.rango, _xlfn.SEQUENCE(4,, 5))),
    _xlpm.MyRow1 &amp; CHAR(10) &amp; _xlpm.MyRow2
 )</f>
-        <v>3C8DB034 8DD2D442 27DF7413 F52EABB4
-4E7C14CD E65BB751 43BFAE5C 3C210173</v>
-      </c>
-      <c r="F10" s="9"/>
-      <c r="G10" s="9"/>
-      <c r="H10" s="9"/>
-      <c r="I10" s="9"/>
-      <c r="J10" s="9"/>
-      <c r="K10" s="9"/>
-      <c r="L10" s="8"/>
-      <c r="N10" s="36">
+        <v>7DAA2CA0 6E6846D8 D74ECABE 65B227FC
+76401883 4B328BD2 C64DA80E DCC12245</v>
+      </c>
+      <c r="I10" s="7"/>
+      <c r="J10" s="7"/>
+      <c r="K10" s="7"/>
+      <c r="L10" s="7"/>
+      <c r="M10" s="7"/>
+      <c r="N10" s="7"/>
+      <c r="O10" s="6"/>
+      <c r="Q10" s="40">
         <v>52</v>
       </c>
-      <c r="O10" s="37" t="str">
+      <c r="R10" s="41" t="str">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="P10" s="36">
+      <c r="S10" s="40">
         <v>69</v>
       </c>
-      <c r="Q10" s="38" t="str">
+      <c r="T10" s="42" t="str">
         <f t="shared" si="1"/>
         <v>E</v>
       </c>
     </row>
-    <row r="11" spans="1:17" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="7" t="str">
-        <f ca="1"/>
-        <v xml:space="preserve">        &lt;Data Hash="4963A7DE"&gt;</v>
-      </c>
-      <c r="D11" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="E11" s="10">
-        <f ca="1">SUM(E7:L7)</f>
+    <row r="11" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D11" s="5" t="str">
+        <f ca="1"/>
+        <v xml:space="preserve">        &lt;Data Hash="71F539A3"&gt;</v>
+      </c>
+      <c r="G11" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="H11" s="8">
+        <f ca="1">SUM(H7:O7)</f>
         <v>64</v>
       </c>
-      <c r="F11" s="9"/>
-      <c r="G11" s="9"/>
-      <c r="H11" s="9"/>
-      <c r="I11" s="9"/>
-      <c r="J11" s="9"/>
-      <c r="K11" s="9"/>
-      <c r="L11" s="8"/>
-      <c r="N11" s="36">
+      <c r="I11" s="7"/>
+      <c r="J11" s="7"/>
+      <c r="K11" s="7"/>
+      <c r="L11" s="7"/>
+      <c r="M11" s="7"/>
+      <c r="N11" s="7"/>
+      <c r="O11" s="6"/>
+      <c r="Q11" s="40">
         <v>53</v>
       </c>
-      <c r="O11" s="37" t="str">
+      <c r="R11" s="41" t="str">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="P11" s="36">
+      <c r="S11" s="40">
         <v>70</v>
       </c>
-      <c r="Q11" s="38" t="str">
+      <c r="T11" s="42" t="str">
         <f t="shared" si="1"/>
         <v>F</v>
       </c>
     </row>
-    <row r="12" spans="1:17" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="12" t="str">
-        <f ca="1"/>
-        <v xml:space="preserve">        3C8DB034 8DD2D442 27DF7413 F52EABB4</v>
-      </c>
-      <c r="D12" s="11" t="s">
-        <v>5</v>
-      </c>
-      <c r="E12" s="10">
+    <row r="12" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D12" s="10" t="str">
+        <f ca="1"/>
+        <v xml:space="preserve">        7DAA2CA0 6E6846D8 D74ECABE 65B227FC</v>
+      </c>
+      <c r="G12" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="H12" s="8">
         <f ca="1">IFERROR(
     ROUND(
-        E11 * LOG(36, 2),
+        H11 * LOG(36, 2),
         2
     ),
     ""
 )</f>
         <v>330.88</v>
       </c>
-      <c r="F12" s="9"/>
-      <c r="G12" s="9"/>
-      <c r="H12" s="9"/>
-      <c r="I12" s="9"/>
-      <c r="J12" s="9"/>
-      <c r="K12" s="9"/>
-      <c r="L12" s="8"/>
-      <c r="N12" s="36">
+      <c r="I12" s="7"/>
+      <c r="J12" s="7"/>
+      <c r="K12" s="7"/>
+      <c r="L12" s="7"/>
+      <c r="M12" s="7"/>
+      <c r="N12" s="7"/>
+      <c r="O12" s="6"/>
+      <c r="Q12" s="40">
         <v>54</v>
       </c>
-      <c r="O12" s="37" t="str">
+      <c r="R12" s="41" t="str">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
     </row>
-    <row r="13" spans="1:17" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="12" t="str">
-        <f ca="1"/>
-        <v xml:space="preserve">        4E7C14CD E65BB751 43BFAE5C 3C210173</v>
-      </c>
-      <c r="D13" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="E13" s="10">
-        <f ca="1">E11*4</f>
+    <row r="13" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D13" s="10" t="str">
+        <f ca="1"/>
+        <v xml:space="preserve">        76401883 4B328BD2 C64DA80E DCC12245</v>
+      </c>
+      <c r="G13" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="H13" s="8">
+        <f ca="1">H11*4</f>
         <v>256</v>
       </c>
-      <c r="F13" s="9"/>
-      <c r="G13" s="9"/>
-      <c r="H13" s="9"/>
-      <c r="I13" s="9"/>
-      <c r="J13" s="9"/>
-      <c r="K13" s="9"/>
-      <c r="L13" s="8"/>
-      <c r="N13" s="36">
+      <c r="I13" s="7"/>
+      <c r="J13" s="7"/>
+      <c r="K13" s="7"/>
+      <c r="L13" s="7"/>
+      <c r="M13" s="7"/>
+      <c r="N13" s="7"/>
+      <c r="O13" s="6"/>
+      <c r="Q13" s="40">
         <v>55</v>
       </c>
-      <c r="O13" s="37" t="str">
+      <c r="R13" s="41" t="str">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
     </row>
-    <row r="14" spans="1:17" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="7" t="str">
+    <row r="14" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D14" s="5" t="str">
         <f ca="1"/>
         <v xml:space="preserve">        &lt;/Data&gt;</v>
       </c>
-      <c r="D14" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="E14" s="26"/>
-      <c r="F14" s="26"/>
-      <c r="G14" s="26"/>
-      <c r="H14" s="26"/>
-      <c r="I14" s="26"/>
-      <c r="J14" s="26"/>
-      <c r="K14" s="26"/>
-      <c r="L14" s="26"/>
-      <c r="N14" s="36">
+      <c r="G14" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="H14" s="24"/>
+      <c r="I14" s="24"/>
+      <c r="J14" s="24"/>
+      <c r="K14" s="24"/>
+      <c r="L14" s="24"/>
+      <c r="M14" s="24"/>
+      <c r="N14" s="24"/>
+      <c r="O14" s="24"/>
+      <c r="Q14" s="40">
         <v>56</v>
       </c>
-      <c r="O14" s="37" t="str">
+      <c r="R14" s="41" t="str">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
     </row>
-    <row r="15" spans="1:17" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="5" t="str">
+    <row r="15" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D15" s="3" t="str">
         <f ca="1"/>
         <v xml:space="preserve">    &lt;/Key&gt;</v>
       </c>
-      <c r="N15" s="36">
+      <c r="Q15" s="40">
         <v>57</v>
       </c>
-      <c r="O15" s="37" t="str">
+      <c r="R15" s="41" t="str">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:17" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="4" t="str">
+    <row r="16" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D16" s="2" t="str">
         <f ca="1"/>
         <v>&lt;/KeyFile&gt;</v>
       </c>
     </row>
-    <row r="17" spans="1:1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="2" t="s">
+    <row r="17" spans="4:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D17" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
+    <row r="18" spans="4:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D18" s="34" t="s">
         <v>0</v>
       </c>
     </row>
+    <row r="19" spans="4:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D19" s="46" t="str">
+        <f>HYPERLINK("https://keepass.info/help/base/keys.html#keyfiles:~:text=XML%20%28recommended%2C%20default%29%2E","https://keepass.info/help/base/keys.html")</f>
+        <v>https://keepass.info/help/base/keys.html</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="C4:L4"/>
-    <mergeCell ref="N4:Q4"/>
+  <mergeCells count="3">
+    <mergeCell ref="F4:O4"/>
+    <mergeCell ref="Q4:T4"/>
+    <mergeCell ref="A4:B4"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="A19" r:id="rId1" location="keyfiles:~:text=XML%20%28recommended%2C%20default%29%2E" xr:uid="{D31E3E2C-0408-4F44-A98B-341A34739836}"/>
+    <hyperlink ref="D19" r:id="rId1" location="keyfiles:~:text=XML%20%28recommended%2C%20default%29%2E" display="https://keepass.info/help/base/keys.html#keyfiles:~:text=XML%20%28recommended%2C%20default%29%2E" xr:uid="{D31E3E2C-0408-4F44-A98B-341A34739836}"/>
   </hyperlinks>
   <pageMargins left="0" right="0" top="0.39370078740157505" bottom="0.39370078740157505" header="0" footer="0"/>
   <pageSetup orientation="portrait" r:id="rId2"/>
@@ -1749,68 +1996,69 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{006B41A7-700D-4541-90D2-F37E6DCAF739}">
-  <sheetPr>
+  <sheetPr codeName="Hoja2">
     <tabColor rgb="FF002060"/>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="B2:K8"/>
+  <dimension ref="A2:Q8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10" defaultRowHeight="30" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10" style="30" customWidth="1"/>
-    <col min="2" max="2" width="53.125" style="30" customWidth="1"/>
-    <col min="3" max="3" width="12.5" style="30" customWidth="1"/>
-    <col min="4" max="6" width="10" style="30" customWidth="1"/>
-    <col min="7" max="7" width="6.375" style="30" customWidth="1"/>
-    <col min="8" max="17" width="10" style="30" customWidth="1"/>
-    <col min="18" max="16384" width="10" style="30"/>
+    <col min="1" max="1" width="10" style="27" customWidth="1"/>
+    <col min="2" max="2" width="53.125" style="29" customWidth="1"/>
+    <col min="3" max="3" width="12.5" style="29" customWidth="1"/>
+    <col min="4" max="6" width="10" style="29" customWidth="1"/>
+    <col min="7" max="7" width="6.375" style="29" customWidth="1"/>
+    <col min="8" max="11" width="10" style="29" customWidth="1"/>
+    <col min="12" max="17" width="10" style="27" customWidth="1"/>
+    <col min="18" max="16384" width="10" style="29"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:11" ht="30" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="B2" s="29" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="3" spans="2:11" ht="75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="31" t="s">
+    <row r="2" spans="2:11" s="29" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="B2" s="28" t="s">
         <v>30</v>
       </c>
-      <c r="F3" s="32" t="s">
+    </row>
+    <row r="3" spans="2:11" s="29" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="30" t="s">
+        <v>40</v>
+      </c>
+      <c r="F3" s="31" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4" spans="2:11" s="29" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="30" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="4" spans="2:11" ht="75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="31" t="s">
+      <c r="H4" s="32" t="s">
+        <v>26</v>
+      </c>
+      <c r="I4" s="32" t="s">
+        <v>25</v>
+      </c>
+      <c r="J4" s="32" t="s">
+        <v>24</v>
+      </c>
+      <c r="K4" s="32"/>
+    </row>
+    <row r="5" spans="2:11" s="29" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="30" t="s">
         <v>29</v>
       </c>
-      <c r="H4" s="33" t="s">
-        <v>27</v>
-      </c>
-      <c r="I4" s="33" t="s">
-        <v>26</v>
-      </c>
-      <c r="J4" s="33" t="s">
-        <v>25</v>
-      </c>
-      <c r="K4" s="33"/>
-    </row>
-    <row r="5" spans="2:11" ht="75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="31" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="6" spans="2:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="32" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="7" spans="2:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="32" t="str">
+    </row>
+    <row r="6" spans="2:11" s="29" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="31" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7" spans="2:11" s="29" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="31" t="str">
         <f ca="1">(_xlfn.CONCAT("©2019 - "&amp;YEAR(TODAY())))</f>
         <v>©2019 - 2026</v>
       </c>
     </row>
-    <row r="8" spans="2:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="32" t="str">
+    <row r="8" spans="2:11" s="29" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="31" t="str">
         <f>_xlfn.CONCAT("GABE PÉREZ / GABEweb")</f>
         <v>GABE PÉREZ / GABEweb</v>
       </c>
